--- a/output/pdf_financials_xlsx/BILD.xlsx
+++ b/output/pdf_financials_xlsx/BILD.xlsx
@@ -3245,22 +3245,22 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>10.395737</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>10.854968</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>11.121785</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>11.32358</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.515195</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>11.610434</v>
       </c>
     </row>
     <row r="93">
@@ -6179,7 +6179,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -7511,7 +7515,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -10216,7 +10224,11 @@
           <t>Share-based payment reserve (note 18)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BILD.xlsx
+++ b/output/pdf_financials_xlsx/BILD.xlsx
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.062595</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.04833</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.019506</v>
       </c>
     </row>
     <row r="13">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.493028</v>
+        <v>-3.555623</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.017966</v>
+        <v>-2.066296</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.396364</v>
+        <v>-2.41587</v>
       </c>
     </row>
     <row r="28">
@@ -1359,13 +1359,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.184484</v>
+        <v>0.121889</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.8438020000000001</v>
+        <v>0.795472</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.828512</v>
+        <v>0.809006</v>
       </c>
     </row>
     <row r="30">
@@ -1395,13 +1395,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.2552373222588268</v>
+        <v>0.1686358815550733</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1.288939222947769</v>
+        <v>1.215113334119506</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.251678807825609</v>
+        <v>1.222210016998866</v>
       </c>
     </row>
     <row r="31">
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-1.433178</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-1.632093</v>
       </c>
     </row>
     <row r="125">
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-1.433178</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-1.632093</v>
       </c>
     </row>
     <row r="126">
@@ -12251,7 +12251,11 @@
           <t>Principal lease payments (note 14)</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -14071,7 +14075,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -14122,7 +14126,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">

--- a/output/pdf_financials_xlsx/BILD.xlsx
+++ b/output/pdf_financials_xlsx/BILD.xlsx
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>0</v>
+        <v>-0.074438</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0</v>
+        <v>-0.007908</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
@@ -10436,7 +10436,11 @@
           <t>Cash, note 4 $ 291,678 $</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -10705,7 +10709,11 @@
           <t>Capital stock, note 5 367,654</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -13316,7 +13324,11 @@
           <t>Share issuance costs, note 5</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E169" s="5" t="n">
         <v>-0.074438</v>
       </c>
